--- a/Examples/Stanford/Input_Data_Sheets/SOIL_parameters.xlsx
+++ b/Examples/Stanford/Input_Data_Sheets/SOIL_parameters.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -81,8 +81,53 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +146,28 @@
         <bgColor theme="0" tint="-0.0499893185216834"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -150,11 +215,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="dashed">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,6 +305,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,993 +741,1695 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="17.5" customWidth="1" style="1" min="1" max="1"/>
-    <col width="12.5" customWidth="1" style="1" min="2" max="2"/>
-    <col width="21.6640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.83203125" customWidth="1" style="1" min="4" max="5"/>
-    <col width="16.33203125" customWidth="1" style="1" min="6" max="6"/>
-    <col width="19.1640625" customWidth="1" style="1" min="7" max="12"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" style="1" min="13" max="14"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="8.83203125" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="26" customWidth="1" style="1" min="1" max="1"/>
+    <col width="12" customWidth="1" style="1" min="2" max="2"/>
+    <col width="14" customWidth="1" style="1" min="3" max="3"/>
+    <col width="12" customWidth="1" style="1" min="4" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" style="1" min="6" max="6"/>
+    <col width="16" customWidth="1" style="1" min="7" max="12"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" style="1" min="13" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" thickBot="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>HydroPol2D - Soil Parameters</t>
-        </is>
-      </c>
-      <c r="M1" s="13" t="n"/>
-      <c r="P1" s="13" t="n"/>
-      <c r="Q1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" thickBot="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" thickBot="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>HydroPol2D Model - Soil Parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1" thickBot="1">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Soil_type</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>ksat (mm/h)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>n [-]</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>alpha [1/m]</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>θsat (cm3.cm-3)</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>θr (cm3.cm-3)</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>θi (cm3.cm-3)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>Sy [-]</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>kgsat (mm/h)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>DTB (m)</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>Ks_multiplier_near_surface</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="22" t="inlineStr">
         <is>
           <t>Ks_multiplier_root_zone</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="22" t="inlineStr">
         <is>
           <t>Ks_multiplier_transmission</t>
         </is>
       </c>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="O2" s="22" t="inlineStr">
+        <is>
+          <t>Ltop_m</t>
+        </is>
+      </c>
+      <c r="P2" s="22" t="inlineStr">
+        <is>
+          <t>dh_max_m</t>
+        </is>
+      </c>
+      <c r="Q2" s="22" t="inlineStr">
+        <is>
+          <t>l_vg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Clay</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="n">
+      <c r="B3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="24" t="n">
         <v>1.09</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="24" t="n">
         <v>0.385</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="24" t="n">
         <v>0.068</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="24" t="n">
         <v>0.0997</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="J3" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="K3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="K3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Silty Clay</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="24" t="n">
         <v>1.23</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="E4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="24" t="n">
         <v>0.423</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="24" t="n">
         <v>0.089</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="24" t="n">
         <v>0.1224</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="24" t="n">
         <v>0.04</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="K4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="K4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Sandy Clay</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="24" t="n">
         <v>1.31</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="24" t="n">
         <v>0.321</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="24" t="n">
         <v>0.075</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="24" t="n">
         <v>0.09959999999999999</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="24" t="n">
         <v>0.06</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="K5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Clay Loam</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="C6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="24" t="n">
         <v>1.31</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="24" t="n">
         <v>1.9</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="24" t="n">
         <v>0.309</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="24" t="n">
         <v>0.095</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="24" t="n">
         <v>0.1164</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="24" t="n">
         <v>0.08</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="K6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Silty Clay Loam</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="C7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="24" t="n">
         <v>1.23</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="24" t="n">
         <v>0.432</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="24" t="n">
         <v>0.089</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="24" t="n">
         <v>0.1233</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="24" t="n">
         <v>0.09</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="K7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Sandy Clay Loam</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="24" t="n">
         <v>1.48</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="24" t="n">
         <v>0.33</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="24" t="n">
         <v>0.0915</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="24" t="n">
         <v>0.11</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="K8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="K8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Silty Loam</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="24" t="n">
         <v>7.6</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="24" t="n">
         <v>1.41</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="24" t="n">
         <v>4.5</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="24" t="n">
         <v>0.434</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="24" t="n">
         <v>0.067</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="24" t="n">
         <v>0.122</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="24" t="n">
         <v>0.14</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="24" t="n">
         <v>152</v>
       </c>
-      <c r="K9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="K9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P9" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Loam</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="24" t="n">
         <v>1.56</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="24" t="n">
         <v>3.6</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="24" t="n">
         <v>0.486</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="24" t="n">
         <v>0.078</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="24" t="n">
         <v>0.1104</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="24" t="n">
         <v>0.18</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="24" t="n">
         <v>68</v>
       </c>
-      <c r="K10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="K10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Sandy Loam</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="24" t="n">
         <v>10.9</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="24" t="n">
         <v>1.89</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="24" t="n">
         <v>0.412</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="24" t="n">
         <v>0.1287</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="24" t="n">
         <v>0.22</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="24" t="n">
         <v>218</v>
       </c>
-      <c r="K11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="K11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Silt</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="24" t="n">
         <v>1.37</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="24" t="n">
         <v>0.486</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="24" t="n">
         <v>0.067</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="24" t="n">
         <v>0.1234</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="24" t="n">
         <v>0.12</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="24" t="n">
         <v>68</v>
       </c>
-      <c r="K12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="K12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P12" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Loamy Sand</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="24" t="n">
         <v>29.9</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="24" t="n">
         <v>2.28</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="24" t="n">
         <v>14.5</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="24" t="n">
         <v>0.401</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="24" t="n">
         <v>0.057</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="24" t="n">
         <v>0.1172</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="24" t="n">
         <v>598</v>
       </c>
-      <c r="K13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="K13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Sand</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="24" t="n">
         <v>117.8</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="24" t="n">
         <v>2.68</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="24" t="n">
         <v>14.5</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="24" t="n">
         <v>0.417</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="24" t="n">
         <v>0.1225</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="24" t="n">
         <v>2356</v>
       </c>
-      <c r="K14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="K14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="24" t="n">
         <v>1.09</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="24" t="n">
         <v>0.385</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="24" t="n">
         <v>0.068</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="24" t="n">
         <v>0.0997</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="5" t="n"/>
+      <c r="K15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P15" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="24" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="5" t="n"/>
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="25" t="n"/>
+      <c r="O16" s="25" t="n"/>
+      <c r="P16" s="25" t="n"/>
+      <c r="Q16" s="25" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="5" t="n"/>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="25" t="n"/>
+      <c r="Q17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="5" t="n"/>
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
+      <c r="M18" s="25" t="n"/>
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="25" t="n"/>
+      <c r="P18" s="25" t="n"/>
+      <c r="Q18" s="25" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="5" t="n"/>
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="25" t="n"/>
+      <c r="L19" s="25" t="n"/>
+      <c r="M19" s="25" t="n"/>
+      <c r="N19" s="25" t="n"/>
+      <c r="O19" s="25" t="n"/>
+      <c r="P19" s="25" t="n"/>
+      <c r="Q19" s="25" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="5" t="n"/>
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="25" t="n"/>
+      <c r="M20" s="25" t="n"/>
+      <c r="N20" s="25" t="n"/>
+      <c r="O20" s="25" t="n"/>
+      <c r="P20" s="25" t="n"/>
+      <c r="Q20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="5" t="n"/>
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="25" t="n"/>
+      <c r="M21" s="25" t="n"/>
+      <c r="N21" s="25" t="n"/>
+      <c r="O21" s="25" t="n"/>
+      <c r="P21" s="25" t="n"/>
+      <c r="Q21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="5" t="n"/>
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="25" t="n"/>
+      <c r="O22" s="25" t="n"/>
+      <c r="P22" s="25" t="n"/>
+      <c r="Q22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="5" t="n"/>
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
+      <c r="Q23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="5" t="n"/>
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="25" t="n"/>
+      <c r="O24" s="25" t="n"/>
+      <c r="P24" s="25" t="n"/>
+      <c r="Q24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="5" t="n"/>
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
+      <c r="N25" s="25" t="n"/>
+      <c r="O25" s="25" t="n"/>
+      <c r="P25" s="25" t="n"/>
+      <c r="Q25" s="25" t="n"/>
     </row>
     <row r="26">
-      <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="5" t="n"/>
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="25" t="n"/>
+      <c r="O26" s="25" t="n"/>
+      <c r="P26" s="25" t="n"/>
+      <c r="Q26" s="25" t="n"/>
     </row>
     <row r="27">
-      <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="5" t="n"/>
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="25" t="n"/>
+      <c r="M27" s="25" t="n"/>
+      <c r="N27" s="25" t="n"/>
+      <c r="O27" s="25" t="n"/>
+      <c r="P27" s="25" t="n"/>
+      <c r="Q27" s="25" t="n"/>
     </row>
     <row r="28">
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="5" t="n"/>
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="25" t="n"/>
+      <c r="M28" s="25" t="n"/>
+      <c r="N28" s="25" t="n"/>
+      <c r="O28" s="25" t="n"/>
+      <c r="P28" s="25" t="n"/>
+      <c r="Q28" s="25" t="n"/>
     </row>
     <row r="29">
-      <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="5" t="n"/>
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="25" t="n"/>
+      <c r="M29" s="25" t="n"/>
+      <c r="N29" s="25" t="n"/>
+      <c r="O29" s="25" t="n"/>
+      <c r="P29" s="25" t="n"/>
+      <c r="Q29" s="25" t="n"/>
     </row>
     <row r="30">
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="5" t="n"/>
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="25" t="n"/>
+      <c r="N30" s="25" t="n"/>
+      <c r="O30" s="25" t="n"/>
+      <c r="P30" s="25" t="n"/>
+      <c r="Q30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="5" t="n"/>
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="25" t="n"/>
+      <c r="M31" s="25" t="n"/>
+      <c r="N31" s="25" t="n"/>
+      <c r="O31" s="25" t="n"/>
+      <c r="P31" s="25" t="n"/>
+      <c r="Q31" s="25" t="n"/>
     </row>
     <row r="32">
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="5" t="n"/>
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="25" t="n"/>
+      <c r="M32" s="25" t="n"/>
+      <c r="N32" s="25" t="n"/>
+      <c r="O32" s="25" t="n"/>
+      <c r="P32" s="25" t="n"/>
+      <c r="Q32" s="25" t="n"/>
     </row>
     <row r="33">
-      <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="5" t="n"/>
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="25" t="n"/>
+      <c r="D33" s="25" t="n"/>
+      <c r="E33" s="25" t="n"/>
+      <c r="F33" s="25" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="25" t="n"/>
+      <c r="M33" s="25" t="n"/>
+      <c r="N33" s="25" t="n"/>
+      <c r="O33" s="25" t="n"/>
+      <c r="P33" s="25" t="n"/>
+      <c r="Q33" s="25" t="n"/>
     </row>
     <row r="34">
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="5" t="n"/>
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="25" t="n"/>
+      <c r="M34" s="25" t="n"/>
+      <c r="N34" s="25" t="n"/>
+      <c r="O34" s="25" t="n"/>
+      <c r="P34" s="25" t="n"/>
+      <c r="Q34" s="25" t="n"/>
     </row>
     <row r="35">
-      <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="5" t="n"/>
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="25" t="n"/>
+      <c r="M35" s="25" t="n"/>
+      <c r="N35" s="25" t="n"/>
+      <c r="O35" s="25" t="n"/>
+      <c r="P35" s="25" t="n"/>
+      <c r="Q35" s="25" t="n"/>
     </row>
     <row r="36">
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="5" t="n"/>
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="25" t="n"/>
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="25" t="n"/>
+      <c r="P36" s="25" t="n"/>
+      <c r="Q36" s="25" t="n"/>
     </row>
     <row r="37">
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="5" t="n"/>
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="25" t="n"/>
+      <c r="M37" s="25" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="O37" s="25" t="n"/>
+      <c r="P37" s="25" t="n"/>
+      <c r="Q37" s="25" t="n"/>
     </row>
     <row r="38">
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="5" t="n"/>
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="25" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="25" t="n"/>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="25" t="n"/>
+      <c r="N38" s="25" t="n"/>
+      <c r="O38" s="25" t="n"/>
+      <c r="P38" s="25" t="n"/>
+      <c r="Q38" s="25" t="n"/>
     </row>
     <row r="39">
-      <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="5" t="n"/>
+      <c r="A39" s="25" t="n"/>
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="25" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="25" t="n"/>
+      <c r="G39" s="25" t="n"/>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="25" t="n"/>
+      <c r="L39" s="25" t="n"/>
+      <c r="M39" s="25" t="n"/>
+      <c r="N39" s="25" t="n"/>
+      <c r="O39" s="25" t="n"/>
+      <c r="P39" s="25" t="n"/>
+      <c r="Q39" s="25" t="n"/>
     </row>
     <row r="40">
-      <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="5" t="n"/>
+      <c r="A40" s="25" t="n"/>
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="25" t="n"/>
+      <c r="L40" s="25" t="n"/>
+      <c r="M40" s="25" t="n"/>
+      <c r="N40" s="25" t="n"/>
+      <c r="O40" s="25" t="n"/>
+      <c r="P40" s="25" t="n"/>
+      <c r="Q40" s="25" t="n"/>
     </row>
     <row r="41">
-      <c r="P41" s="4" t="n"/>
-      <c r="Q41" s="5" t="n"/>
+      <c r="A41" s="25" t="n"/>
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="25" t="n"/>
+      <c r="D41" s="25" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="25" t="n"/>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="25" t="n"/>
+      <c r="L41" s="25" t="n"/>
+      <c r="M41" s="25" t="n"/>
+      <c r="N41" s="25" t="n"/>
+      <c r="O41" s="25" t="n"/>
+      <c r="P41" s="25" t="n"/>
+      <c r="Q41" s="25" t="n"/>
     </row>
     <row r="42">
-      <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="5" t="n"/>
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="25" t="n"/>
+      <c r="L42" s="25" t="n"/>
+      <c r="M42" s="25" t="n"/>
+      <c r="N42" s="25" t="n"/>
+      <c r="O42" s="25" t="n"/>
+      <c r="P42" s="25" t="n"/>
+      <c r="Q42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="5" t="n"/>
+      <c r="A43" s="25" t="n"/>
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="25" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="25" t="n"/>
+      <c r="L43" s="25" t="n"/>
+      <c r="M43" s="25" t="n"/>
+      <c r="N43" s="25" t="n"/>
+      <c r="O43" s="25" t="n"/>
+      <c r="P43" s="25" t="n"/>
+      <c r="Q43" s="25" t="n"/>
     </row>
     <row r="44">
-      <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="5" t="n"/>
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="25" t="n"/>
+      <c r="M44" s="25" t="n"/>
+      <c r="N44" s="25" t="n"/>
+      <c r="O44" s="25" t="n"/>
+      <c r="P44" s="25" t="n"/>
+      <c r="Q44" s="25" t="n"/>
     </row>
     <row r="45">
-      <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="5" t="n"/>
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="25" t="n"/>
+      <c r="L45" s="25" t="n"/>
+      <c r="M45" s="25" t="n"/>
+      <c r="N45" s="25" t="n"/>
+      <c r="O45" s="25" t="n"/>
+      <c r="P45" s="25" t="n"/>
+      <c r="Q45" s="25" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-      <c r="L46" s="8" t="n"/>
-      <c r="M46" s="8" t="n"/>
-      <c r="N46" s="8" t="n"/>
-      <c r="O46" s="8" t="n"/>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="5" t="n"/>
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="25" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="25" t="n"/>
+      <c r="F46" s="25" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="25" t="n"/>
+      <c r="L46" s="25" t="n"/>
+      <c r="M46" s="25" t="n"/>
+      <c r="N46" s="25" t="n"/>
+      <c r="O46" s="25" t="n"/>
+      <c r="P46" s="25" t="n"/>
+      <c r="Q46" s="25" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="n"/>
+      <c r="B47" s="25" t="n"/>
+      <c r="C47" s="25" t="n"/>
+      <c r="D47" s="25" t="n"/>
+      <c r="E47" s="25" t="n"/>
+      <c r="F47" s="25" t="n"/>
+      <c r="G47" s="25" t="n"/>
+      <c r="H47" s="25" t="n"/>
+      <c r="I47" s="25" t="n"/>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="25" t="n"/>
+      <c r="L47" s="25" t="n"/>
+      <c r="M47" s="25" t="n"/>
+      <c r="N47" s="25" t="n"/>
+      <c r="O47" s="25" t="n"/>
+      <c r="P47" s="25" t="n"/>
+      <c r="Q47" s="25" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="n"/>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="25" t="n"/>
+      <c r="D48" s="25" t="n"/>
+      <c r="E48" s="25" t="n"/>
+      <c r="F48" s="25" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="25" t="n"/>
+      <c r="M48" s="25" t="n"/>
+      <c r="N48" s="25" t="n"/>
+      <c r="O48" s="25" t="n"/>
+      <c r="P48" s="25" t="n"/>
+      <c r="Q48" s="25" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="n"/>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="25" t="n"/>
+      <c r="L49" s="25" t="n"/>
+      <c r="M49" s="25" t="n"/>
+      <c r="N49" s="25" t="n"/>
+      <c r="O49" s="25" t="n"/>
+      <c r="P49" s="25" t="n"/>
+      <c r="Q49" s="25" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="n"/>
+      <c r="B50" s="25" t="n"/>
+      <c r="C50" s="25" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="25" t="n"/>
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="25" t="n"/>
+      <c r="M50" s="25" t="n"/>
+      <c r="N50" s="25" t="n"/>
+      <c r="O50" s="25" t="n"/>
+      <c r="P50" s="25" t="n"/>
+      <c r="Q50" s="25" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="25" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="25" t="n"/>
+      <c r="L51" s="25" t="n"/>
+      <c r="M51" s="25" t="n"/>
+      <c r="N51" s="25" t="n"/>
+      <c r="O51" s="25" t="n"/>
+      <c r="P51" s="25" t="n"/>
+      <c r="Q51" s="25" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="25" t="n"/>
+      <c r="C52" s="25" t="n"/>
+      <c r="D52" s="25" t="n"/>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="25" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
+      <c r="I52" s="25" t="n"/>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="25" t="n"/>
+      <c r="M52" s="25" t="n"/>
+      <c r="N52" s="25" t="n"/>
+      <c r="O52" s="25" t="n"/>
+      <c r="P52" s="25" t="n"/>
+      <c r="Q52" s="25" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="n"/>
+      <c r="B53" s="25" t="n"/>
+      <c r="C53" s="25" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="25" t="n"/>
+      <c r="F53" s="25" t="n"/>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="25" t="n"/>
+      <c r="I53" s="25" t="n"/>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="25" t="n"/>
+      <c r="L53" s="25" t="n"/>
+      <c r="M53" s="25" t="n"/>
+      <c r="N53" s="25" t="n"/>
+      <c r="O53" s="25" t="n"/>
+      <c r="P53" s="25" t="n"/>
+      <c r="Q53" s="25" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="n"/>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="25" t="n"/>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
+      <c r="M54" s="25" t="n"/>
+      <c r="N54" s="25" t="n"/>
+      <c r="O54" s="25" t="n"/>
+      <c r="P54" s="25" t="n"/>
+      <c r="Q54" s="25" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="n"/>
+      <c r="B55" s="25" t="n"/>
+      <c r="C55" s="25" t="n"/>
+      <c r="D55" s="25" t="n"/>
+      <c r="E55" s="25" t="n"/>
+      <c r="F55" s="25" t="n"/>
+      <c r="G55" s="25" t="n"/>
+      <c r="H55" s="25" t="n"/>
+      <c r="I55" s="25" t="n"/>
+      <c r="J55" s="25" t="n"/>
+      <c r="K55" s="25" t="n"/>
+      <c r="L55" s="25" t="n"/>
+      <c r="M55" s="25" t="n"/>
+      <c r="N55" s="25" t="n"/>
+      <c r="O55" s="25" t="n"/>
+      <c r="P55" s="25" t="n"/>
+      <c r="Q55" s="25" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="n"/>
+      <c r="B56" s="25" t="n"/>
+      <c r="C56" s="25" t="n"/>
+      <c r="D56" s="25" t="n"/>
+      <c r="E56" s="25" t="n"/>
+      <c r="F56" s="25" t="n"/>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="25" t="n"/>
+      <c r="I56" s="25" t="n"/>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="25" t="n"/>
+      <c r="L56" s="25" t="n"/>
+      <c r="M56" s="25" t="n"/>
+      <c r="N56" s="25" t="n"/>
+      <c r="O56" s="25" t="n"/>
+      <c r="P56" s="25" t="n"/>
+      <c r="Q56" s="25" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="n"/>
+      <c r="B57" s="25" t="n"/>
+      <c r="C57" s="25" t="n"/>
+      <c r="D57" s="25" t="n"/>
+      <c r="E57" s="25" t="n"/>
+      <c r="F57" s="25" t="n"/>
+      <c r="G57" s="25" t="n"/>
+      <c r="H57" s="25" t="n"/>
+      <c r="I57" s="25" t="n"/>
+      <c r="J57" s="25" t="n"/>
+      <c r="K57" s="25" t="n"/>
+      <c r="L57" s="25" t="n"/>
+      <c r="M57" s="25" t="n"/>
+      <c r="N57" s="25" t="n"/>
+      <c r="O57" s="25" t="n"/>
+      <c r="P57" s="25" t="n"/>
+      <c r="Q57" s="25" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="n"/>
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="25" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="25" t="n"/>
+      <c r="F58" s="25" t="n"/>
+      <c r="G58" s="25" t="n"/>
+      <c r="H58" s="25" t="n"/>
+      <c r="I58" s="25" t="n"/>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="25" t="n"/>
+      <c r="L58" s="25" t="n"/>
+      <c r="M58" s="25" t="n"/>
+      <c r="N58" s="25" t="n"/>
+      <c r="O58" s="25" t="n"/>
+      <c r="P58" s="25" t="n"/>
+      <c r="Q58" s="25" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="n"/>
+      <c r="B59" s="25" t="n"/>
+      <c r="C59" s="25" t="n"/>
+      <c r="D59" s="25" t="n"/>
+      <c r="E59" s="25" t="n"/>
+      <c r="F59" s="25" t="n"/>
+      <c r="G59" s="25" t="n"/>
+      <c r="H59" s="25" t="n"/>
+      <c r="I59" s="25" t="n"/>
+      <c r="J59" s="25" t="n"/>
+      <c r="K59" s="25" t="n"/>
+      <c r="L59" s="25" t="n"/>
+      <c r="M59" s="25" t="n"/>
+      <c r="N59" s="25" t="n"/>
+      <c r="O59" s="25" t="n"/>
+      <c r="P59" s="25" t="n"/>
+      <c r="Q59" s="25" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="n"/>
+      <c r="B60" s="25" t="n"/>
+      <c r="C60" s="25" t="n"/>
+      <c r="D60" s="25" t="n"/>
+      <c r="E60" s="25" t="n"/>
+      <c r="F60" s="25" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="25" t="n"/>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="25" t="n"/>
+      <c r="L60" s="25" t="n"/>
+      <c r="M60" s="25" t="n"/>
+      <c r="N60" s="25" t="n"/>
+      <c r="O60" s="25" t="n"/>
+      <c r="P60" s="25" t="n"/>
+      <c r="Q60" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Examples/Stanford/Input_Data_Sheets/SOIL_parameters.xlsx
+++ b/Examples/Stanford/Input_Data_Sheets/SOIL_parameters.xlsx
@@ -423,58 +423,106 @@
     <author>Marcus Gomes</author>
   </authors>
   <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Soil class name, for your reference only.</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Soil class code. It must match the cell values of the SOIL raster (SOIL_path in General_Data). One row per class.</t>
+      </text>
+    </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Marcus Gomes:
-Saturated Hydraulic Conductivity </t>
+Saturated hydraulic conductivity of the soil, in mm/h. Used for infiltration and for drainage through the three soil layers; the three Ks multipliers scale it per layer.</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-van-Genutchen n parameter</t>
+        <t xml:space="preserve">Marcus Gomes:
+van Genuchten n of the soil (dimensionless, greater than 1).</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-van-Genutchen alpha parameter</t>
+        <t xml:space="preserve">Marcus Gomes:
+van Genuchten alpha of the soil, in 1/m.</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-Saturated porosity</t>
+        <t xml:space="preserve">Marcus Gomes:
+Saturated water content (porosity) of the soil, cm3/cm3.</t>
       </text>
     </comment>
     <comment ref="G2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-Residual porosity</t>
+        <t xml:space="preserve">Marcus Gomes:
+Residual water content of the soil, cm3/cm3.</t>
       </text>
     </comment>
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-Initial water content</t>
+        <t xml:space="preserve">Marcus Gomes:
+Initial water content of the soil layers at the start of the run, cm3/cm3, between the residual and saturated values.</t>
       </text>
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-Shallow aquifer drainable porosity</t>
+        <t xml:space="preserve">Marcus Gomes:
+Specific yield (drainable porosity) of the shallow aquifer. Legacy groundwater only. The layered subsurface ignores this column: Sy comes from each layer's van Genuchten curve (theta_sat minus the water content at field capacity).</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-Lateral saturated hydraulic conductivity for shallow aquifer</t>
+        <t xml:space="preserve">Marcus Gomes:
+Lateral saturated hydraulic conductivity of the shallow aquifer, in mm/h. Legacy groundwater: the aquifer conductivity. Layered subsurface: the horizontal conductivity of the rock layers when regolith_ksat_h_mm_h and RegolithKsatH_path (General_Data) are empty.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
-        <t>Marcus Gomes:
-Distance to bedrock</t>
+        <t xml:space="preserve">Marcus Gomes:
+Depth to bedrock per soil class, in metres. Not read by the current MATLAB code: the soil depth comes from DTB_path, or 1 m when DTB_path is empty.</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Multiplier of ksat in the near-surface soil layer (thickness Ltop_m). Use less than 1 for crusted or compacted surfaces. 1 = no change.</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Multiplier of ksat in the root-zone soil layer (from Ltop_m down to the root depth of LULC_parameters.xlsx). 1 = no change.</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Multiplier of ksat in the transmission soil layer (from the root depth down to the bottom of the soil). 1 = no change.</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Thickness of the near-surface soil layer, in metres. It is also the length scale of the infiltration capacity: C = Ks x [min(h0 - h(theta), dh_max) / Ltop + 1].</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Cap on the driving head difference in the infiltration capacity, in metres: C = Ks x [min(h0 - h(theta), dh_max) / Ltop + 1]. Default 1 m.</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Marcus Gomes:
+Mualem pore-connectivity parameter l of the van Genuchten-Mualem unsaturated conductivity (dimensionless; 0.5 is the usual value).</t>
       </text>
     </comment>
   </commentList>
